--- a/Pruebas calificadas/COLEGIO-BUENAVISTA-(IED)-1101_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-BUENAVISTA-(IED)-1101_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2321,11 +2297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -2333,7 +2305,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -2586,7 +2554,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -2839,7 +2803,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -3092,7 +3052,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -3345,7 +3301,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -3598,7 +3550,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -3851,7 +3799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -4104,7 +4048,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4345,11 +4289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -4357,7 +4297,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4598,11 +4538,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -4610,7 +4546,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4851,11 +4787,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -4863,7 +4795,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5104,11 +5036,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -5116,7 +5044,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5357,11 +5285,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -5369,7 +5293,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5610,11 +5534,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -5622,7 +5542,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5863,11 +5783,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -5875,7 +5791,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6116,11 +6032,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -6128,7 +6040,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6369,11 +6281,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -6381,7 +6289,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6542,11 +6450,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -6554,7 +6458,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6795,11 +6699,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -6807,7 +6707,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7048,11 +6948,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -7060,7 +6956,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7301,11 +7197,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -7313,7 +7205,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7554,11 +7446,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -7566,7 +7454,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7807,11 +7695,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -7819,7 +7703,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8060,11 +7944,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -8072,7 +7952,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8313,11 +8193,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -8325,7 +8201,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8566,11 +8442,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -8578,7 +8450,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8819,11 +8691,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -8831,7 +8699,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9072,11 +8940,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -9084,7 +8948,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9325,11 +9189,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -9337,7 +9197,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9578,11 +9438,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -9590,7 +9446,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9831,11 +9687,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -9843,7 +9695,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10080,11 +9932,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -10092,7 +9940,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10333,11 +10181,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -10345,7 +10189,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10582,11 +10426,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -10594,7 +10434,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10835,11 +10675,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -10847,7 +10683,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11088,11 +10924,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -11100,7 +10932,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11341,11 +11173,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -11353,7 +11181,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11594,11 +11422,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -11606,7 +11430,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11847,11 +11671,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -11859,7 +11679,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12100,11 +11920,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -12112,7 +11928,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12353,11 +12169,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -12365,7 +12177,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12606,11 +12418,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -12618,7 +12426,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12859,11 +12667,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -12871,7 +12675,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13112,11 +12916,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -13124,7 +12924,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13365,11 +13165,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -13377,7 +13173,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13618,11 +13414,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -13630,7 +13422,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13871,11 +13663,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -13883,7 +13671,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14124,11 +13912,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -14136,7 +13920,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14377,11 +14161,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -14389,7 +14169,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14550,11 +14330,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -14562,7 +14338,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14803,11 +14579,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -14815,7 +14587,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15056,11 +14828,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -15068,7 +14836,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15309,11 +15077,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -15321,7 +15085,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15562,11 +15326,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -15574,7 +15334,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15815,11 +15575,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -15827,7 +15583,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16064,11 +15820,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -16076,7 +15828,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16317,11 +16069,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -16329,7 +16077,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16570,11 +16318,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -16582,7 +16326,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-BUENAVISTA-(IED)-1101_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-BUENAVISTA-(IED)-1101_CALIFICADO.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ65"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>LESLY SOFIA VILLALBA SANCHEZ</t>
+          <t>MAIKOL SEBASTIAN CASTRO VELASQUEZ</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1029280271</t>
+          <t>1027526800</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -6313,139 +6313,219 @@
           <t>LENGUAJE</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AD24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AK24" s="2" t="inlineStr"/>
+      <c r="AK24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AM24" s="2" t="inlineStr"/>
+      <c r="AM24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AO24" s="2" t="inlineStr"/>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AQ24" s="2" t="inlineStr"/>
-      <c r="AR24" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AS24" s="2" t="inlineStr"/>
-      <c r="AT24" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AU24" s="2" t="inlineStr"/>
+      <c r="AQ24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR24" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AT24" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AW24" s="5">
-        <f>COUNTIF(J24:AV24,"CORRECTO")</f>
+        <f>COUNTIF(J25:AV25,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX24" s="5">
-        <f>COUNTIF(J24:AV24,"INCORRECTO")</f>
+        <f>COUNTIF(J25:AV25,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY24" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ24" s="6">
-        <f>AW24/AY24</f>
+        <f>AW25/AY25</f>
         <v/>
       </c>
     </row>
@@ -6463,12 +6543,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>MAIKOL SEBASTIAN CASTRO VELASQUEZ</t>
+          <t>MARIA FERNANDA VEGA LUGO</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1027526800</t>
+          <t>1031134603</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -6484,22 +6564,22 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -6534,17 +6614,17 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
@@ -6564,7 +6644,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
@@ -6574,22 +6654,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AB25" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB25" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AD25" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD25" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AE25" s="2" t="inlineStr">
@@ -6604,22 +6684,22 @@
       </c>
       <c r="AG25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AH25" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH25" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AI25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AJ25" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ25" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AK25" s="2" t="inlineStr">
@@ -6634,17 +6714,17 @@
       </c>
       <c r="AM25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AN25" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AO25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
@@ -6664,17 +6744,17 @@
       </c>
       <c r="AS25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AT25" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AU25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AV25" s="3" t="inlineStr">
@@ -6683,18 +6763,18 @@
         </is>
       </c>
       <c r="AW25" s="5">
-        <f>COUNTIF(J25:AV25,"CORRECTO")</f>
+        <f>COUNTIF(J26:AV26,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX25" s="5">
-        <f>COUNTIF(J25:AV25,"INCORRECTO")</f>
+        <f>COUNTIF(J26:AV26,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY25" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ25" s="6">
-        <f>AW25/AY25</f>
+        <f>AW26/AY26</f>
         <v/>
       </c>
     </row>
@@ -6712,12 +6792,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA VEGA LUGO</t>
+          <t>MICHEL CONTRERAS RENDON</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1031134603</t>
+          <t>1033728604</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -6733,12 +6813,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -6753,12 +6833,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -6813,7 +6893,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
@@ -6823,12 +6903,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AB26" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -6843,12 +6923,12 @@
       </c>
       <c r="AE26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AF26" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AF26" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AG26" s="2" t="inlineStr">
@@ -6873,12 +6953,12 @@
       </c>
       <c r="AK26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AL26" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AL26" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AM26" s="2" t="inlineStr">
@@ -6893,12 +6973,12 @@
       </c>
       <c r="AO26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP26" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AQ26" s="2" t="inlineStr">
@@ -6913,37 +6993,37 @@
       </c>
       <c r="AS26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AT26" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AU26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AV26" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV26" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AW26" s="5">
-        <f>COUNTIF(J26:AV26,"CORRECTO")</f>
+        <f>COUNTIF(J27:AV27,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX26" s="5">
-        <f>COUNTIF(J26:AV26,"INCORRECTO")</f>
+        <f>COUNTIF(J27:AV27,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY26" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ26" s="6">
-        <f>AW26/AY26</f>
+        <f>AW27/AY27</f>
         <v/>
       </c>
     </row>
@@ -6961,12 +7041,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>MICHEL CONTRERAS RENDON</t>
+          <t>MIGUEL ANGEL FAJARDO LOAIZA</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1033728604</t>
+          <t>1025541524</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -6982,12 +7062,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -7002,12 +7082,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -7181,18 +7261,18 @@
         </is>
       </c>
       <c r="AW27" s="5">
-        <f>COUNTIF(J27:AV27,"CORRECTO")</f>
+        <f>COUNTIF(J28:AV28,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX27" s="5">
-        <f>COUNTIF(J27:AV27,"INCORRECTO")</f>
+        <f>COUNTIF(J28:AV28,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY27" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ27" s="6">
-        <f>AW27/AY27</f>
+        <f>AW28/AY28</f>
         <v/>
       </c>
     </row>
@@ -7210,12 +7290,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL FAJARDO LOAIZA</t>
+          <t>NIXON ADRIAN SANCHEZ MIGUEZ</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1025541524</t>
+          <t>1146884131</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -7311,7 +7391,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -7321,7 +7401,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
@@ -7430,18 +7510,18 @@
         </is>
       </c>
       <c r="AW28" s="5">
-        <f>COUNTIF(J28:AV28,"CORRECTO")</f>
+        <f>COUNTIF(J29:AV29,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX28" s="5">
-        <f>COUNTIF(J28:AV28,"INCORRECTO")</f>
+        <f>COUNTIF(J29:AV29,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY28" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ28" s="6">
-        <f>AW28/AY28</f>
+        <f>AW29/AY29</f>
         <v/>
       </c>
     </row>
@@ -7459,12 +7539,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>NIXON ADRIAN SANCHEZ MIGUEZ</t>
+          <t>SARA JULIANY MURILLO VALDES</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1146884131</t>
+          <t>1028868292</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -7480,12 +7560,12 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -7540,7 +7620,7 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
@@ -7560,7 +7640,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
@@ -7590,12 +7670,12 @@
       </c>
       <c r="AE29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AF29" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AG29" s="2" t="inlineStr">
@@ -7679,18 +7759,18 @@
         </is>
       </c>
       <c r="AW29" s="5">
-        <f>COUNTIF(J29:AV29,"CORRECTO")</f>
+        <f>COUNTIF(J30:AV30,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX29" s="5">
-        <f>COUNTIF(J29:AV29,"INCORRECTO")</f>
+        <f>COUNTIF(J30:AV30,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY29" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ29" s="6">
-        <f>AW29/AY29</f>
+        <f>AW30/AY30</f>
         <v/>
       </c>
     </row>
@@ -7708,12 +7788,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>SARA JULIANY MURILLO VALDES</t>
+          <t>SEBASTIAN DAVID RUIZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1028868292</t>
+          <t>1011104268</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -7729,12 +7809,12 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -7789,7 +7869,7 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -7809,7 +7889,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -7819,12 +7899,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AB30" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB30" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -7839,12 +7919,12 @@
       </c>
       <c r="AE30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AF30" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AF30" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AG30" s="2" t="inlineStr">
@@ -7928,18 +8008,18 @@
         </is>
       </c>
       <c r="AW30" s="5">
-        <f>COUNTIF(J30:AV30,"CORRECTO")</f>
+        <f>COUNTIF(J31:AV31,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX30" s="5">
-        <f>COUNTIF(J30:AV30,"INCORRECTO")</f>
+        <f>COUNTIF(J31:AV31,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY30" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ30" s="6">
-        <f>AW30/AY30</f>
+        <f>AW31/AY31</f>
         <v/>
       </c>
     </row>
@@ -7957,12 +8037,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>SEBASTIAN DAVID RUIZ RODRIGUEZ</t>
+          <t>YUIBARI MATIAS TANDIOY CHASOY</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1011104268</t>
+          <t>1016718403</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -8008,12 +8088,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8058,7 +8138,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -8068,12 +8148,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AB31" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -8177,18 +8257,18 @@
         </is>
       </c>
       <c r="AW31" s="5">
-        <f>COUNTIF(J31:AV31,"CORRECTO")</f>
+        <f>COUNTIF(J32:AV32,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX31" s="5">
-        <f>COUNTIF(J31:AV31,"INCORRECTO")</f>
+        <f>COUNTIF(J32:AV32,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY31" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ31" s="6">
-        <f>AW31/AY31</f>
+        <f>AW32/AY32</f>
         <v/>
       </c>
     </row>
@@ -8206,12 +8286,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>YUIBARI MATIAS TANDIOY CHASOY</t>
+          <t>ZARA JIRETH GRISALES PEREZ</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1016718403</t>
+          <t>1011324941</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -8247,17 +8327,17 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -8307,7 +8387,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -8317,12 +8397,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AB32" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB32" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -8377,12 +8457,12 @@
       </c>
       <c r="AM32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AN32" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AO32" s="2" t="inlineStr">
@@ -8426,18 +8506,18 @@
         </is>
       </c>
       <c r="AW32" s="5">
-        <f>COUNTIF(J32:AV32,"CORRECTO")</f>
+        <f>COUNTIF(J33:AV33,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX32" s="5">
-        <f>COUNTIF(J32:AV32,"INCORRECTO")</f>
+        <f>COUNTIF(J33:AV33,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY32" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ32" s="6">
-        <f>AW32/AY32</f>
+        <f>AW33/AY33</f>
         <v/>
       </c>
     </row>
@@ -8455,12 +8535,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ZARA JIRETH GRISALES PEREZ</t>
+          <t>ALISSON REYES IBARRA</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1011324941</t>
+          <t>1023384160</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -8471,12 +8551,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>LENGUAJE</t>
+          <t>MATEMÁTICAS</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -8489,24 +8569,24 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -8516,27 +8596,27 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="R33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="T33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -8546,7 +8626,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
@@ -8566,7 +8646,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AB33" s="4" t="inlineStr">
@@ -8576,7 +8656,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AD33" s="4" t="inlineStr">
@@ -8586,7 +8666,7 @@
       </c>
       <c r="AE33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AF33" s="4" t="inlineStr">
@@ -8596,97 +8676,97 @@
       </c>
       <c r="AG33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AH33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AI33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AJ33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AK33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AL33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AM33" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN33" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AO33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AP33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AQ33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AR33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AS33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AT33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AU33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AV33" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AW33" s="5">
-        <f>COUNTIF(J33:AV33,"CORRECTO")</f>
+        <f>COUNTIF(J34:AV34,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX33" s="5">
-        <f>COUNTIF(J33:AV33,"INCORRECTO")</f>
+        <f>COUNTIF(J34:AV34,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY33" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ33" s="6">
-        <f>AW33/AY33</f>
+        <f>AW34/AY34</f>
         <v/>
       </c>
     </row>
@@ -8704,12 +8784,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ALISSON REYES IBARRA</t>
+          <t>ANGEL DANIEL RAMIREZ VENTO</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1023384160</t>
+          <t>1025325941</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -8745,37 +8825,37 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
@@ -8785,12 +8865,12 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -8805,22 +8885,22 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z34" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AB34" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -8845,7 +8925,7 @@
       </c>
       <c r="AG34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
@@ -8885,7 +8965,7 @@
       </c>
       <c r="AO34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
@@ -8895,7 +8975,7 @@
       </c>
       <c r="AQ34" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
@@ -8905,7 +8985,7 @@
       </c>
       <c r="AS34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
@@ -8924,18 +9004,18 @@
         </is>
       </c>
       <c r="AW34" s="5">
-        <f>COUNTIF(J34:AV34,"CORRECTO")</f>
+        <f>COUNTIF(J35:AV35,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX34" s="5">
-        <f>COUNTIF(J34:AV34,"INCORRECTO")</f>
+        <f>COUNTIF(J35:AV35,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY34" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ34" s="6">
-        <f>AW34/AY34</f>
+        <f>AW35/AY35</f>
         <v/>
       </c>
     </row>
@@ -8953,12 +9033,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ANGEL DANIEL RAMIREZ VENTO</t>
+          <t>ANGIE CATALINA PERDOMO MORENO</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1025325941</t>
+          <t>1033734882</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -8974,17 +9054,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -9004,12 +9084,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9024,7 +9104,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -9044,7 +9124,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
@@ -9074,27 +9154,27 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AD35" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AE35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AF35" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AG35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
@@ -9104,22 +9184,22 @@
       </c>
       <c r="AI35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AJ35" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ35" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AK35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AL35" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL35" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AM35" s="2" t="inlineStr">
@@ -9134,12 +9214,12 @@
       </c>
       <c r="AO35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP35" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AQ35" s="2" t="inlineStr">
@@ -9154,7 +9234,7 @@
       </c>
       <c r="AS35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
@@ -9164,7 +9244,7 @@
       </c>
       <c r="AU35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AV35" s="3" t="inlineStr">
@@ -9173,18 +9253,18 @@
         </is>
       </c>
       <c r="AW35" s="5">
-        <f>COUNTIF(J35:AV35,"CORRECTO")</f>
+        <f>COUNTIF(J36:AV36,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX35" s="5">
-        <f>COUNTIF(J35:AV35,"INCORRECTO")</f>
+        <f>COUNTIF(J36:AV36,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY35" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ35" s="6">
-        <f>AW35/AY35</f>
+        <f>AW36/AY36</f>
         <v/>
       </c>
     </row>
@@ -9202,12 +9282,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ANGIE CATALINA PERDOMO MORENO</t>
+          <t>ANTHONY JAVIER RODRIGUEZ SIERRA</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1033734882</t>
+          <t>1029284078</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -9223,7 +9303,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -9233,27 +9313,27 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -9273,12 +9353,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9293,7 +9373,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -9313,7 +9393,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
@@ -9343,12 +9423,12 @@
       </c>
       <c r="AG36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AH36" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH36" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AI36" s="2" t="inlineStr">
@@ -9363,12 +9443,12 @@
       </c>
       <c r="AK36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AL36" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AM36" s="2" t="inlineStr">
@@ -9393,7 +9473,7 @@
       </c>
       <c r="AQ36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
@@ -9413,27 +9493,27 @@
       </c>
       <c r="AU36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AV36" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV36" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AW36" s="5">
-        <f>COUNTIF(J36:AV36,"CORRECTO")</f>
+        <f>COUNTIF(J37:AV37,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX36" s="5">
-        <f>COUNTIF(J36:AV36,"INCORRECTO")</f>
+        <f>COUNTIF(J37:AV37,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY36" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ36" s="6">
-        <f>AW36/AY36</f>
+        <f>AW37/AY37</f>
         <v/>
       </c>
     </row>
@@ -9451,12 +9531,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ANTHONY JAVIER RODRIGUEZ SIERRA</t>
+          <t>CAROL DAYANA MORERA VELANDIA</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1029284078</t>
+          <t>1032680642</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -9472,7 +9552,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -9482,22 +9562,18 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -9512,12 +9588,12 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="R37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -9532,12 +9608,12 @@
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="V37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -9552,12 +9628,12 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="Z37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -9572,7 +9648,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AD37" s="3" t="inlineStr">
@@ -9582,62 +9658,62 @@
       </c>
       <c r="AE37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AF37" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF37" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AG37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AH37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AI37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AJ37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AK37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AL37" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL37" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AM37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AN37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AO37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AP37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AQ37" s="2" t="inlineStr">
@@ -9652,7 +9728,7 @@
       </c>
       <c r="AS37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
@@ -9662,27 +9738,27 @@
       </c>
       <c r="AU37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AV37" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AW37" s="5">
-        <f>COUNTIF(J37:AV37,"CORRECTO")</f>
+        <f>COUNTIF(J38:AV38,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX37" s="5">
-        <f>COUNTIF(J37:AV37,"INCORRECTO")</f>
+        <f>COUNTIF(J38:AV38,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY37" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ37" s="6">
-        <f>AW37/AY37</f>
+        <f>AW38/AY38</f>
         <v/>
       </c>
     </row>
@@ -9700,12 +9776,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CAROL DAYANA MORERA VELANDIA</t>
+          <t>DANNA VALENTINA RAMIREZ CASAS</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1032680642</t>
+          <t>1029282437</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -9721,17 +9797,17 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -9739,7 +9815,11 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
@@ -9747,42 +9827,42 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -9797,12 +9877,12 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z38" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -9817,7 +9897,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AD38" s="3" t="inlineStr">
@@ -9827,17 +9907,17 @@
       </c>
       <c r="AE38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AF38" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AG38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
@@ -9847,7 +9927,7 @@
       </c>
       <c r="AI38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
@@ -9857,17 +9937,17 @@
       </c>
       <c r="AK38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AL38" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AM38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AN38" s="3" t="inlineStr">
@@ -9887,7 +9967,7 @@
       </c>
       <c r="AQ38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
@@ -9907,7 +9987,7 @@
       </c>
       <c r="AU38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AV38" s="3" t="inlineStr">
@@ -9916,18 +9996,18 @@
         </is>
       </c>
       <c r="AW38" s="5">
-        <f>COUNTIF(J38:AV38,"CORRECTO")</f>
+        <f>COUNTIF(J39:AV39,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX38" s="5">
-        <f>COUNTIF(J38:AV38,"INCORRECTO")</f>
+        <f>COUNTIF(J39:AV39,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY38" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ38" s="6">
-        <f>AW38/AY38</f>
+        <f>AW39/AY39</f>
         <v/>
       </c>
     </row>
@@ -9945,12 +10025,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>DANNA VALENTINA RAMIREZ CASAS</t>
+          <t>DAVID LEONARDO CARDENAS POLOCHE</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1029282437</t>
+          <t>1011104165</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -9976,17 +10056,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -9996,29 +10076,25 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="P39" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="R39" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr"/>
       <c r="T39" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
@@ -10026,12 +10102,12 @@
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="V39" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -10056,17 +10132,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AB39" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB39" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AD39" s="3" t="inlineStr">
@@ -10086,7 +10162,7 @@
       </c>
       <c r="AG39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
@@ -10096,12 +10172,12 @@
       </c>
       <c r="AI39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AJ39" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ39" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AK39" s="2" t="inlineStr">
@@ -10126,7 +10202,7 @@
       </c>
       <c r="AO39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
@@ -10136,7 +10212,7 @@
       </c>
       <c r="AQ39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
@@ -10146,37 +10222,37 @@
       </c>
       <c r="AS39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT39" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AU39" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AV39" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV39" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AW39" s="5">
-        <f>COUNTIF(J39:AV39,"CORRECTO")</f>
+        <f>COUNTIF(J40:AV40,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX39" s="5">
-        <f>COUNTIF(J39:AV39,"INCORRECTO")</f>
+        <f>COUNTIF(J40:AV40,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY39" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ39" s="6">
-        <f>AW39/AY39</f>
+        <f>AW40/AY40</f>
         <v/>
       </c>
     </row>
@@ -10194,12 +10270,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>DAVID LEONARDO CARDENAS POLOCHE</t>
+          <t>DAVID SANTIAGO OLMOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1011104165</t>
+          <t>1012920785</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -10225,27 +10301,27 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -10255,7 +10331,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
@@ -10263,7 +10339,11 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
@@ -10301,12 +10381,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AB40" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -10321,7 +10401,7 @@
       </c>
       <c r="AE40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -10331,7 +10411,7 @@
       </c>
       <c r="AG40" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
@@ -10341,12 +10421,12 @@
       </c>
       <c r="AI40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AJ40" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AK40" s="2" t="inlineStr">
@@ -10371,7 +10451,7 @@
       </c>
       <c r="AO40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
@@ -10381,7 +10461,7 @@
       </c>
       <c r="AQ40" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
@@ -10391,12 +10471,12 @@
       </c>
       <c r="AS40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AT40" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AU40" s="2" t="inlineStr">
@@ -10410,18 +10490,18 @@
         </is>
       </c>
       <c r="AW40" s="5">
-        <f>COUNTIF(J40:AV40,"CORRECTO")</f>
+        <f>COUNTIF(J41:AV41,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX40" s="5">
-        <f>COUNTIF(J40:AV40,"INCORRECTO")</f>
+        <f>COUNTIF(J41:AV41,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY40" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ40" s="6">
-        <f>AW40/AY40</f>
+        <f>AW41/AY41</f>
         <v/>
       </c>
     </row>
@@ -10439,12 +10519,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>DAVID SANTIAGO OLMOS RODRIGUEZ</t>
+          <t>EDISON FABIAN GARCIA BERNAL</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1012920785</t>
+          <t>1028867580</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -10470,47 +10550,47 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
@@ -10550,17 +10630,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AB41" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB41" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AD41" s="3" t="inlineStr">
@@ -10570,7 +10650,7 @@
       </c>
       <c r="AE41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -10580,7 +10660,7 @@
       </c>
       <c r="AG41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
@@ -10590,37 +10670,37 @@
       </c>
       <c r="AI41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AJ41" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ41" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AK41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AL41" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL41" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AM41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN41" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AO41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
@@ -10659,18 +10739,18 @@
         </is>
       </c>
       <c r="AW41" s="5">
-        <f>COUNTIF(J41:AV41,"CORRECTO")</f>
+        <f>COUNTIF(J42:AV42,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX41" s="5">
-        <f>COUNTIF(J41:AV41,"INCORRECTO")</f>
+        <f>COUNTIF(J42:AV42,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY41" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ41" s="6">
-        <f>AW41/AY41</f>
+        <f>AW42/AY42</f>
         <v/>
       </c>
     </row>
@@ -10688,12 +10768,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>EDISON FABIAN GARCIA BERNAL</t>
+          <t>ELKIN MATEO ROZO RODRÍGUEZ</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1028867580</t>
+          <t>1019765693</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -10719,32 +10799,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="P42" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10779,7 +10859,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
@@ -10789,22 +10869,22 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="Z42" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AB42" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -10829,7 +10909,7 @@
       </c>
       <c r="AG42" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
@@ -10839,12 +10919,12 @@
       </c>
       <c r="AI42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AJ42" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AK42" s="2" t="inlineStr">
@@ -10869,7 +10949,7 @@
       </c>
       <c r="AO42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
@@ -10889,12 +10969,12 @@
       </c>
       <c r="AS42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT42" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AU42" s="2" t="inlineStr">
@@ -10908,18 +10988,18 @@
         </is>
       </c>
       <c r="AW42" s="5">
-        <f>COUNTIF(J42:AV42,"CORRECTO")</f>
+        <f>COUNTIF(J43:AV43,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX42" s="5">
-        <f>COUNTIF(J42:AV42,"INCORRECTO")</f>
+        <f>COUNTIF(J43:AV43,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY42" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ42" s="6">
-        <f>AW42/AY42</f>
+        <f>AW43/AY43</f>
         <v/>
       </c>
     </row>
@@ -10937,12 +11017,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>ELKIN MATEO ROZO RODRÍGUEZ</t>
+          <t>EMILY JULIANA IBAÑEZ MONTOYA</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1019765693</t>
+          <t>1034402231</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
@@ -10958,37 +11038,37 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N43" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -10998,32 +11078,32 @@
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="R43" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T43" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -11058,7 +11138,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AD43" s="3" t="inlineStr">
@@ -11068,7 +11148,7 @@
       </c>
       <c r="AE43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -11078,7 +11158,7 @@
       </c>
       <c r="AG43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
@@ -11098,37 +11178,37 @@
       </c>
       <c r="AK43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AL43" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AM43" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AN43" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AO43" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP43" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AQ43" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
@@ -11138,37 +11218,37 @@
       </c>
       <c r="AS43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AT43" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AU43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AV43" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AW43" s="5">
-        <f>COUNTIF(J43:AV43,"CORRECTO")</f>
+        <f>COUNTIF(J44:AV44,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX43" s="5">
-        <f>COUNTIF(J43:AV43,"INCORRECTO")</f>
+        <f>COUNTIF(J44:AV44,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY43" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ43" s="6">
-        <f>AW43/AY43</f>
+        <f>AW44/AY44</f>
         <v/>
       </c>
     </row>
@@ -11186,12 +11266,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>EMILY JULIANA IBAÑEZ MONTOYA</t>
+          <t>ESTEBAN ALEJANDRO ALBA LINAREZ</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1034402231</t>
+          <t>1028868450</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -11207,12 +11287,12 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -11247,7 +11327,7 @@
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
@@ -11257,37 +11337,37 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
@@ -11307,7 +11387,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AD44" s="3" t="inlineStr">
@@ -11327,27 +11407,27 @@
       </c>
       <c r="AG44" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AH44" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH44" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AI44" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AJ44" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ44" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AK44" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AL44" s="3" t="inlineStr">
@@ -11367,17 +11447,17 @@
       </c>
       <c r="AO44" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AP44" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AQ44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
@@ -11406,18 +11486,18 @@
         </is>
       </c>
       <c r="AW44" s="5">
-        <f>COUNTIF(J44:AV44,"CORRECTO")</f>
+        <f>COUNTIF(J45:AV45,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX44" s="5">
-        <f>COUNTIF(J44:AV44,"INCORRECTO")</f>
+        <f>COUNTIF(J45:AV45,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY44" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ44" s="6">
-        <f>AW44/AY44</f>
+        <f>AW45/AY45</f>
         <v/>
       </c>
     </row>
@@ -11435,12 +11515,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>ESTEBAN ALEJANDRO ALBA LINAREZ</t>
+          <t>GELEN ESTEFANIA BOHORQUEZ PUENTES</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1028868450</t>
+          <t>1023899067</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -11486,22 +11566,22 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -11516,7 +11596,7 @@
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -11526,32 +11606,32 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="X45" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z45" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AB45" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB45" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -11566,7 +11646,7 @@
       </c>
       <c r="AE45" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -11576,12 +11656,12 @@
       </c>
       <c r="AG45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AH45" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AI45" s="2" t="inlineStr">
@@ -11596,7 +11676,7 @@
       </c>
       <c r="AK45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AL45" s="3" t="inlineStr">
@@ -11616,17 +11696,17 @@
       </c>
       <c r="AO45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP45" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AQ45" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
@@ -11646,27 +11726,27 @@
       </c>
       <c r="AU45" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV45" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AW45" s="5">
-        <f>COUNTIF(J45:AV45,"CORRECTO")</f>
+        <f>COUNTIF(J46:AV46,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX45" s="5">
-        <f>COUNTIF(J45:AV45,"INCORRECTO")</f>
+        <f>COUNTIF(J46:AV46,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY45" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ45" s="6">
-        <f>AW45/AY45</f>
+        <f>AW46/AY46</f>
         <v/>
       </c>
     </row>
@@ -11684,12 +11764,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>GELEN ESTEFANIA BOHORQUEZ PUENTES</t>
+          <t>HEIDY SARAHI AVILA SALAZAR</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1023899067</t>
+          <t>1033716721</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -11805,7 +11885,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AD46" s="3" t="inlineStr">
@@ -11825,7 +11905,7 @@
       </c>
       <c r="AG46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
@@ -11855,27 +11935,27 @@
       </c>
       <c r="AM46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN46" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AO46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AP46" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AQ46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
@@ -11895,27 +11975,27 @@
       </c>
       <c r="AU46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AV46" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AW46" s="5">
-        <f>COUNTIF(J46:AV46,"CORRECTO")</f>
+        <f>COUNTIF(J47:AV47,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX46" s="5">
-        <f>COUNTIF(J46:AV46,"INCORRECTO")</f>
+        <f>COUNTIF(J47:AV47,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY46" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ46" s="6">
-        <f>AW46/AY46</f>
+        <f>AW47/AY47</f>
         <v/>
       </c>
     </row>
@@ -11933,12 +12013,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>HEIDY SARAHI AVILA SALAZAR</t>
+          <t>JIRETH SOFIA GALVIS RUGELES</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1033716721</t>
+          <t>1025541773</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -11994,17 +12074,17 @@
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="R47" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
@@ -12014,17 +12094,17 @@
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="V47" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V47" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
@@ -12034,27 +12114,27 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="Z47" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AB47" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AD47" s="3" t="inlineStr">
@@ -12064,7 +12144,7 @@
       </c>
       <c r="AE47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
@@ -12094,12 +12174,12 @@
       </c>
       <c r="AK47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AL47" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL47" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AM47" s="2" t="inlineStr">
@@ -12114,7 +12194,7 @@
       </c>
       <c r="AO47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
@@ -12134,17 +12214,17 @@
       </c>
       <c r="AS47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AT47" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT47" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AU47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AV47" s="3" t="inlineStr">
@@ -12153,18 +12233,18 @@
         </is>
       </c>
       <c r="AW47" s="5">
-        <f>COUNTIF(J47:AV47,"CORRECTO")</f>
+        <f>COUNTIF(J48:AV48,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX47" s="5">
-        <f>COUNTIF(J47:AV47,"INCORRECTO")</f>
+        <f>COUNTIF(J48:AV48,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY47" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ47" s="6">
-        <f>AW47/AY47</f>
+        <f>AW48/AY48</f>
         <v/>
       </c>
     </row>
@@ -12182,12 +12262,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>JIRETH SOFIA GALVIS RUGELES</t>
+          <t>JOEL SEBASTIAN PUENTES MURCIA</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1025541773</t>
+          <t>1013129719</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -12223,12 +12303,12 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -12243,17 +12323,17 @@
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R48" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr">
@@ -12273,7 +12353,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
@@ -12283,17 +12363,17 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="Z48" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z48" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
@@ -12313,17 +12393,17 @@
       </c>
       <c r="AE48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AF48" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF48" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AG48" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
@@ -12333,12 +12413,12 @@
       </c>
       <c r="AI48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AJ48" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AK48" s="2" t="inlineStr">
@@ -12373,7 +12453,7 @@
       </c>
       <c r="AQ48" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
@@ -12393,27 +12473,27 @@
       </c>
       <c r="AU48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV48" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AW48" s="5">
-        <f>COUNTIF(J48:AV48,"CORRECTO")</f>
+        <f>COUNTIF(J49:AV49,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX48" s="5">
-        <f>COUNTIF(J48:AV48,"INCORRECTO")</f>
+        <f>COUNTIF(J49:AV49,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY48" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ48" s="6">
-        <f>AW48/AY48</f>
+        <f>AW49/AY49</f>
         <v/>
       </c>
     </row>
@@ -12431,12 +12511,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>JOEL SEBASTIAN PUENTES MURCIA</t>
+          <t>JOSTIN DANNIEL PRIETO CERON</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1013129719</t>
+          <t>1034665336</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -12452,22 +12532,22 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -12482,12 +12562,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="P49" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12512,17 +12592,17 @@
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="V49" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="3" t="inlineStr">
@@ -12552,7 +12632,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AD49" s="3" t="inlineStr">
@@ -12582,12 +12662,12 @@
       </c>
       <c r="AI49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AJ49" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ49" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AK49" s="2" t="inlineStr">
@@ -12612,7 +12692,7 @@
       </c>
       <c r="AO49" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AP49" s="3" t="inlineStr">
@@ -12622,7 +12702,7 @@
       </c>
       <c r="AQ49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AR49" s="3" t="inlineStr">
@@ -12632,37 +12712,37 @@
       </c>
       <c r="AS49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AT49" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AU49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AV49" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AW49" s="5">
-        <f>COUNTIF(J49:AV49,"CORRECTO")</f>
+        <f>COUNTIF(J50:AV50,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX49" s="5">
-        <f>COUNTIF(J49:AV49,"INCORRECTO")</f>
+        <f>COUNTIF(J50:AV50,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY49" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ49" s="6">
-        <f>AW49/AY49</f>
+        <f>AW50/AY50</f>
         <v/>
       </c>
     </row>
@@ -12680,12 +12760,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>JOSTIN DANNIEL PRIETO CERON</t>
+          <t>JUAN CAMILO CASTRO MATEUS</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1034665336</t>
+          <t>1033723727</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
@@ -12701,42 +12781,42 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N50" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P50" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12751,7 +12831,7 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="T50" s="3" t="inlineStr">
@@ -12761,17 +12841,17 @@
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="V50" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V50" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr">
@@ -12801,12 +12881,12 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AD50" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD50" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AE50" s="2" t="inlineStr">
@@ -12821,7 +12901,7 @@
       </c>
       <c r="AG50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AH50" s="3" t="inlineStr">
@@ -12841,12 +12921,12 @@
       </c>
       <c r="AK50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AL50" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AM50" s="2" t="inlineStr">
@@ -12861,12 +12941,12 @@
       </c>
       <c r="AO50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP50" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AQ50" s="2" t="inlineStr">
@@ -12881,7 +12961,7 @@
       </c>
       <c r="AS50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AT50" s="3" t="inlineStr">
@@ -12891,27 +12971,27 @@
       </c>
       <c r="AU50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AV50" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV50" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AW50" s="5">
-        <f>COUNTIF(J50:AV50,"CORRECTO")</f>
+        <f>COUNTIF(J51:AV51,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX50" s="5">
-        <f>COUNTIF(J50:AV50,"INCORRECTO")</f>
+        <f>COUNTIF(J51:AV51,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY50" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ50" s="6">
-        <f>AW50/AY50</f>
+        <f>AW51/AY51</f>
         <v/>
       </c>
     </row>
@@ -12929,12 +13009,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>JUAN CAMILO CASTRO MATEUS</t>
+          <t>JUAN DAVID GUATIVA PARRA</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1033723727</t>
+          <t>1076242863</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
@@ -12950,22 +13030,22 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -12980,12 +13060,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="P51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -13000,7 +13080,7 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T51" s="3" t="inlineStr">
@@ -13020,7 +13100,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr">
@@ -13030,17 +13110,17 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="Z51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
@@ -13050,27 +13130,27 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AD51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AE51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AF51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AG51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AH51" s="3" t="inlineStr">
@@ -13080,47 +13160,47 @@
       </c>
       <c r="AI51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AJ51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AK51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AL51" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL51" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AM51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AN51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AO51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AP51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AQ51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AR51" s="3" t="inlineStr">
@@ -13130,37 +13210,37 @@
       </c>
       <c r="AS51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT51" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AU51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AV51" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AW51" s="5">
-        <f>COUNTIF(J51:AV51,"CORRECTO")</f>
+        <f>COUNTIF(J52:AV52,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX51" s="5">
-        <f>COUNTIF(J51:AV51,"INCORRECTO")</f>
+        <f>COUNTIF(J52:AV52,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY51" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ51" s="6">
-        <f>AW51/AY51</f>
+        <f>AW52/AY52</f>
         <v/>
       </c>
     </row>
@@ -13178,12 +13258,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>JUAN DAVID GUATIVA PARRA</t>
+          <t>KAREN JULIETH MENDOZA FRANCO</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1076242863</t>
+          <t>1027527826</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -13199,37 +13279,37 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -13249,12 +13329,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="T52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -13269,27 +13349,27 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Z52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
@@ -13299,7 +13379,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AD52" s="3" t="inlineStr">
@@ -13309,7 +13389,7 @@
       </c>
       <c r="AE52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AF52" s="3" t="inlineStr">
@@ -13319,47 +13399,47 @@
       </c>
       <c r="AG52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AH52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AI52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AJ52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AK52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AL52" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AM52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AO52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AP52" s="3" t="inlineStr">
@@ -13389,27 +13469,27 @@
       </c>
       <c r="AU52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AV52" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV52" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AW52" s="5">
-        <f>COUNTIF(J52:AV52,"CORRECTO")</f>
+        <f>COUNTIF(J53:AV53,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX52" s="5">
-        <f>COUNTIF(J52:AV52,"INCORRECTO")</f>
+        <f>COUNTIF(J53:AV53,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY52" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ52" s="6">
-        <f>AW52/AY52</f>
+        <f>AW53/AY53</f>
         <v/>
       </c>
     </row>
@@ -13427,12 +13507,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>KAREN JULIETH MENDOZA FRANCO</t>
+          <t>KEVIN ALEXANDER VILLAMIL TRILLOS</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1027527826</t>
+          <t>1023912049</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
@@ -13478,7 +13558,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
@@ -13498,12 +13578,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="T53" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T53" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -13548,12 +13628,12 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AD53" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD53" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AE53" s="2" t="inlineStr">
@@ -13588,7 +13668,7 @@
       </c>
       <c r="AK53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AL53" s="3" t="inlineStr">
@@ -13608,17 +13688,17 @@
       </c>
       <c r="AO53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP53" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AQ53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
@@ -13628,37 +13708,37 @@
       </c>
       <c r="AS53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AT53" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AU53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AV53" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AW53" s="5">
-        <f>COUNTIF(J53:AV53,"CORRECTO")</f>
+        <f>COUNTIF(J54:AV54,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX53" s="5">
-        <f>COUNTIF(J53:AV53,"INCORRECTO")</f>
+        <f>COUNTIF(J54:AV54,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY53" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ53" s="6">
-        <f>AW53/AY53</f>
+        <f>AW54/AY54</f>
         <v/>
       </c>
     </row>
@@ -13676,12 +13756,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>KEVIN ALEXANDER VILLAMIL TRILLOS</t>
+          <t>LEIDY JIMENA GUTIERREZ MATEUS</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1023912049</t>
+          <t>1031541715</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
@@ -13697,12 +13777,12 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -13717,22 +13797,22 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N54" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P54" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -13757,37 +13837,37 @@
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="X54" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="Z54" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
@@ -13797,22 +13877,22 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AD54" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AE54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AF54" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF54" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AG54" s="2" t="inlineStr">
@@ -13827,17 +13907,17 @@
       </c>
       <c r="AI54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AJ54" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AK54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AL54" s="3" t="inlineStr">
@@ -13847,12 +13927,12 @@
       </c>
       <c r="AM54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AN54" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AO54" s="2" t="inlineStr">
@@ -13867,7 +13947,7 @@
       </c>
       <c r="AQ54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
@@ -13877,17 +13957,17 @@
       </c>
       <c r="AS54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AT54" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT54" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AU54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AV54" s="3" t="inlineStr">
@@ -13896,18 +13976,18 @@
         </is>
       </c>
       <c r="AW54" s="5">
-        <f>COUNTIF(J54:AV54,"CORRECTO")</f>
+        <f>COUNTIF(J55:AV55,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX54" s="5">
-        <f>COUNTIF(J54:AV54,"INCORRECTO")</f>
+        <f>COUNTIF(J55:AV55,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY54" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ54" s="6">
-        <f>AW54/AY54</f>
+        <f>AW55/AY55</f>
         <v/>
       </c>
     </row>
@@ -13925,12 +14005,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>LEIDY JIMENA GUTIERREZ MATEUS</t>
+          <t>MAIKOL SEBASTIAN CASTRO VELASQUEZ</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1031541715</t>
+          <t>1027526800</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
@@ -13946,22 +14026,22 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -13996,7 +14076,7 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="T55" s="3" t="inlineStr">
@@ -14026,7 +14106,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Z55" s="3" t="inlineStr">
@@ -14036,17 +14116,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AB55" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB55" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AD55" s="3" t="inlineStr">
@@ -14056,22 +14136,22 @@
       </c>
       <c r="AE55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AF55" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AG55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AH55" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AI55" s="2" t="inlineStr">
@@ -14086,17 +14166,17 @@
       </c>
       <c r="AK55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AL55" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL55" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AM55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AN55" s="3" t="inlineStr">
@@ -14106,12 +14186,12 @@
       </c>
       <c r="AO55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AP55" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AQ55" s="2" t="inlineStr">
@@ -14126,17 +14206,17 @@
       </c>
       <c r="AS55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AT55" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AU55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AV55" s="3" t="inlineStr">
@@ -14145,18 +14225,18 @@
         </is>
       </c>
       <c r="AW55" s="5">
-        <f>COUNTIF(J55:AV55,"CORRECTO")</f>
+        <f>COUNTIF(J57:AV57,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX55" s="5">
-        <f>COUNTIF(J55:AV55,"INCORRECTO")</f>
+        <f>COUNTIF(J57:AV57,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY55" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ55" s="6">
-        <f>AW55/AY55</f>
+        <f>AW57/AY57</f>
         <v/>
       </c>
     </row>
@@ -14174,12 +14254,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>LESLY SOFIA VILLALBA SANCHEZ</t>
+          <t>MARIA FERNANDA VEGA LUGO</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1029280271</t>
+          <t>1031134603</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -14193,139 +14273,219 @@
           <t>MATEMÁTICAS</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="U56" s="2" t="inlineStr"/>
-      <c r="V56" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="W56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V56" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AD56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="AF56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AK56" s="2" t="inlineStr"/>
+      <c r="AK56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AL56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AM56" s="2" t="inlineStr"/>
+      <c r="AM56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="AN56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AO56" s="2" t="inlineStr"/>
+      <c r="AO56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AQ56" s="2" t="inlineStr"/>
-      <c r="AR56" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AS56" s="2" t="inlineStr"/>
+      <c r="AQ56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR56" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AU56" s="2" t="inlineStr"/>
+      <c r="AU56" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="AV56" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AW56" s="5">
-        <f>COUNTIF(J56:AV56,"CORRECTO")</f>
+        <f>COUNTIF(J58:AV58,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX56" s="5">
-        <f>COUNTIF(J56:AV56,"INCORRECTO")</f>
+        <f>COUNTIF(J58:AV58,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY56" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ56" s="6">
-        <f>AW56/AY56</f>
+        <f>AW58/AY58</f>
         <v/>
       </c>
     </row>
@@ -14343,12 +14503,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>MAIKOL SEBASTIAN CASTRO VELASQUEZ</t>
+          <t>MICHEL CONTRERAS RENDON</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1027526800</t>
+          <t>1033728604</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
@@ -14374,7 +14534,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
@@ -14394,22 +14554,22 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="P57" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="R57" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
@@ -14434,12 +14594,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="X57" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -14454,27 +14614,27 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AB57" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AD57" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD57" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AE57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
@@ -14484,17 +14644,17 @@
       </c>
       <c r="AG57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AH57" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH57" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AI57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AJ57" s="3" t="inlineStr">
@@ -14514,12 +14674,12 @@
       </c>
       <c r="AM57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN57" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AO57" s="2" t="inlineStr">
@@ -14534,17 +14694,17 @@
       </c>
       <c r="AQ57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AR57" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR57" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AS57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
@@ -14554,7 +14714,7 @@
       </c>
       <c r="AU57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AV57" s="3" t="inlineStr">
@@ -14563,18 +14723,18 @@
         </is>
       </c>
       <c r="AW57" s="5">
-        <f>COUNTIF(J57:AV57,"CORRECTO")</f>
+        <f>COUNTIF(J59:AV59,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX57" s="5">
-        <f>COUNTIF(J57:AV57,"INCORRECTO")</f>
+        <f>COUNTIF(J59:AV59,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY57" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ57" s="6">
-        <f>AW57/AY57</f>
+        <f>AW59/AY59</f>
         <v/>
       </c>
     </row>
@@ -14592,12 +14752,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA VEGA LUGO</t>
+          <t>MIGUEL ANGEL FAJARDO LOAIZA</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1031134603</t>
+          <t>1025541524</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
@@ -14613,12 +14773,12 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -14643,27 +14803,27 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr">
@@ -14683,22 +14843,22 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="X58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Z58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -14713,27 +14873,27 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AD58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AE58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AF58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AG58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AH58" s="3" t="inlineStr">
@@ -14743,42 +14903,42 @@
       </c>
       <c r="AI58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AJ58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AK58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AL58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AM58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AO58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AP58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AQ58" s="2" t="inlineStr">
@@ -14793,7 +14953,7 @@
       </c>
       <c r="AS58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
@@ -14803,27 +14963,27 @@
       </c>
       <c r="AU58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AV58" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV58" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AW58" s="5">
-        <f>COUNTIF(J58:AV58,"CORRECTO")</f>
+        <f>COUNTIF(J60:AV60,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX58" s="5">
-        <f>COUNTIF(J58:AV58,"INCORRECTO")</f>
+        <f>COUNTIF(J60:AV60,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY58" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ58" s="6">
-        <f>AW58/AY58</f>
+        <f>AW60/AY60</f>
         <v/>
       </c>
     </row>
@@ -14841,12 +15001,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>MICHEL CONTRERAS RENDON</t>
+          <t>NIXON ADRIAN SANCHEZ MIGUEZ</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1033728604</t>
+          <t>1146884131</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
@@ -14862,22 +15022,22 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -14892,42 +15052,42 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P59" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="R59" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R59" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="T59" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T59" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V59" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V59" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -14942,37 +15102,37 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="Z59" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z59" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AB59" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB59" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AD59" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AE59" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
@@ -14982,17 +15142,17 @@
       </c>
       <c r="AG59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AH59" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AI59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AJ59" s="3" t="inlineStr">
@@ -15002,12 +15162,12 @@
       </c>
       <c r="AK59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AL59" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AM59" s="2" t="inlineStr">
@@ -15022,7 +15182,7 @@
       </c>
       <c r="AO59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
@@ -15042,7 +15202,7 @@
       </c>
       <c r="AS59" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
@@ -15061,18 +15221,18 @@
         </is>
       </c>
       <c r="AW59" s="5">
-        <f>COUNTIF(J59:AV59,"CORRECTO")</f>
+        <f>COUNTIF(J61:AV61,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX59" s="5">
-        <f>COUNTIF(J59:AV59,"INCORRECTO")</f>
+        <f>COUNTIF(J61:AV61,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY59" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ59" s="6">
-        <f>AW59/AY59</f>
+        <f>AW61/AY61</f>
         <v/>
       </c>
     </row>
@@ -15090,12 +15250,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL FAJARDO LOAIZA</t>
+          <t>SARA JULIANY MURILLO VALDES</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1025541524</t>
+          <t>1028868292</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
@@ -15129,11 +15289,7 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
@@ -15161,7 +15317,7 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T60" s="3" t="inlineStr">
@@ -15201,7 +15357,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
@@ -15211,42 +15367,42 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AD60" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AE60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AF60" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AG60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AH60" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH60" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AI60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AJ60" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AK60" s="2" t="inlineStr">
@@ -15271,32 +15427,32 @@
       </c>
       <c r="AO60" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AP60" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AQ60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AR60" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AS60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AT60" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT60" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AU60" s="2" t="inlineStr">
@@ -15310,18 +15466,18 @@
         </is>
       </c>
       <c r="AW60" s="5">
-        <f>COUNTIF(J60:AV60,"CORRECTO")</f>
+        <f>COUNTIF(J62:AV62,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX60" s="5">
-        <f>COUNTIF(J60:AV60,"INCORRECTO")</f>
+        <f>COUNTIF(J62:AV62,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY60" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ60" s="6">
-        <f>AW60/AY60</f>
+        <f>AW62/AY62</f>
         <v/>
       </c>
     </row>
@@ -15339,12 +15495,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>NIXON ADRIAN SANCHEZ MIGUEZ</t>
+          <t>SEBASTIAN DAVID RUIZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1146884131</t>
+          <t>1011104268</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
@@ -15470,12 +15626,12 @@
       </c>
       <c r="AE61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AF61" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF61" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AG61" s="2" t="inlineStr">
@@ -15530,12 +15686,12 @@
       </c>
       <c r="AQ61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AR61" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AS61" s="2" t="inlineStr">
@@ -15559,18 +15715,18 @@
         </is>
       </c>
       <c r="AW61" s="5">
-        <f>COUNTIF(J61:AV61,"CORRECTO")</f>
+        <f>COUNTIF(J63:AV63,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX61" s="5">
-        <f>COUNTIF(J61:AV61,"INCORRECTO")</f>
+        <f>COUNTIF(J63:AV63,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY61" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ61" s="6">
-        <f>AW61/AY61</f>
+        <f>AW63/AY63</f>
         <v/>
       </c>
     </row>
@@ -15588,12 +15744,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>SARA JULIANY MURILLO VALDES</t>
+          <t>YUIBARI MATIAS TANDIOY CHASOY</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1028868292</t>
+          <t>1016718403</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
@@ -15609,12 +15765,12 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -15627,7 +15783,11 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
           <t>INCORRECTO</t>
@@ -15635,12 +15795,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="P62" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -15655,12 +15815,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="T62" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T62" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -15675,12 +15835,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="X62" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -15705,7 +15865,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AD62" s="3" t="inlineStr">
@@ -15715,7 +15875,7 @@
       </c>
       <c r="AE62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AF62" s="3" t="inlineStr">
@@ -15725,22 +15885,22 @@
       </c>
       <c r="AG62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AH62" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH62" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AI62" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AJ62" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ62" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AK62" s="2" t="inlineStr">
@@ -15765,12 +15925,12 @@
       </c>
       <c r="AO62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AP62" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP62" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AQ62" s="2" t="inlineStr">
@@ -15785,12 +15945,12 @@
       </c>
       <c r="AS62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AT62" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AU62" s="2" t="inlineStr">
@@ -15804,18 +15964,18 @@
         </is>
       </c>
       <c r="AW62" s="5">
-        <f>COUNTIF(J62:AV62,"CORRECTO")</f>
+        <f>COUNTIF(J64:AV64,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX62" s="5">
-        <f>COUNTIF(J62:AV62,"INCORRECTO")</f>
+        <f>COUNTIF(J64:AV64,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY62" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ62" s="6">
-        <f>AW62/AY62</f>
+        <f>AW64/AY64</f>
         <v/>
       </c>
     </row>
@@ -15833,12 +15993,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>SEBASTIAN DAVID RUIZ RODRIGUEZ</t>
+          <t>ZARA JIRETH GRISALES PEREZ</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>1011104268</t>
+          <t>1011324941</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
@@ -15854,42 +16014,42 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N63" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="P63" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -15904,32 +16064,32 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="T63" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="V63" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="X63" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -15944,12 +16104,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AB63" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -15964,17 +16124,17 @@
       </c>
       <c r="AE63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AF63" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AG63" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AH63" s="3" t="inlineStr">
@@ -15994,12 +16154,12 @@
       </c>
       <c r="AK63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AL63" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL63" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AM63" s="2" t="inlineStr">
@@ -16014,17 +16174,17 @@
       </c>
       <c r="AO63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AP63" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP63" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AQ63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AR63" s="3" t="inlineStr">
@@ -16034,17 +16194,17 @@
       </c>
       <c r="AS63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AT63" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT63" s="4" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AU63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AV63" s="3" t="inlineStr">
@@ -16053,515 +16213,17 @@
         </is>
       </c>
       <c r="AW63" s="5">
-        <f>COUNTIF(J63:AV63,"CORRECTO")</f>
+        <f>COUNTIF(J65:AV65,"CORRECTO")</f>
         <v/>
       </c>
       <c r="AX63" s="5">
-        <f>COUNTIF(J63:AV63,"INCORRECTO")</f>
+        <f>COUNTIF(J65:AV65,"INCORRECTO")</f>
         <v/>
       </c>
       <c r="AY63" s="5" t="n">
         <v>20</v>
       </c>
       <c r="AZ63" s="6">
-        <f>AW63/AY63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>111001100013</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>YUIBARI MATIAS TANDIOY CHASOY</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>1016718403</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>1101</v>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>MATEMÁTICAS</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N64" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="P64" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="R64" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="S64" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="U64" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="W64" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="X64" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y64" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="Z64" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AB64" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AD64" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AE64" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AF64" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AG64" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AH64" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AI64" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AJ64" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="AK64" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AL64" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="AM64" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AN64" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="AO64" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AP64" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="AQ64" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AR64" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AS64" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AT64" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AU64" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AV64" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="AW64" s="5">
-        <f>COUNTIF(J64:AV64,"CORRECTO")</f>
-        <v/>
-      </c>
-      <c r="AX64" s="5">
-        <f>COUNTIF(J64:AV64,"INCORRECTO")</f>
-        <v/>
-      </c>
-      <c r="AY64" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ64" s="6">
-        <f>AW64/AY64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>111001100013</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>ZARA JIRETH GRISALES PEREZ</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>1011324941</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>1101</v>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>MATEMÁTICAS</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N65" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="P65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="R65" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="S65" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="T65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="U65" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="W65" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="X65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y65" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="Z65" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AB65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AD65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AE65" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AF65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AG65" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AH65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AI65" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AJ65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AK65" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AL65" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="AM65" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AN65" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="AO65" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AP65" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="AQ65" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AR65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AS65" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AT65" s="4" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
-        </is>
-      </c>
-      <c r="AU65" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AV65" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AW65" s="5">
-        <f>COUNTIF(J65:AV65,"CORRECTO")</f>
-        <v/>
-      </c>
-      <c r="AX65" s="5">
-        <f>COUNTIF(J65:AV65,"INCORRECTO")</f>
-        <v/>
-      </c>
-      <c r="AY65" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ65" s="6">
         <f>AW65/AY65</f>
         <v/>
       </c>
